--- a/0_Documents/Kalkulation/Arbeitsaufzeichnung.xlsx
+++ b/0_Documents/Kalkulation/Arbeitsaufzeichnung.xlsx
@@ -8,38 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\Lumify\0_Documents\Kalkulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC60A68-CB0D-4B12-BDCA-8F6627A9A174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7597D078-D0EA-4D7C-B8CE-5EC30E6CDEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{42DB02A7-F323-4E09-A6DB-68C0AF5073E0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Datum</t>
   </si>
@@ -56,6 +37,9 @@
     <t>Tätigkeit</t>
   </si>
   <si>
+    <t>Projektstruktur (Backend/Frontend) / Music-Provider</t>
+  </si>
+  <si>
     <t>User-System / Friendship-System</t>
   </si>
   <si>
@@ -74,32 +58,50 @@
     <t>ModalProviders / Recents-Module / FeatureControllers</t>
   </si>
   <si>
+    <t>Sidebar / Feature Todos / TodoBoard</t>
+  </si>
+  <si>
+    <t>Feature Events / Kalender-Grid &amp; Logik / EventModal</t>
+  </si>
+  <si>
+    <t>SpaceSwitcher / FeatureNavigation / Übersetzer-Util (FlatDB)</t>
+  </si>
+  <si>
+    <t>Feature Notes / TreeView / FileView (PathBar, SearchBar, ActionLine)</t>
+  </si>
+  <si>
+    <t>Testprojekt / Unit-Tests (Todos, Events, Notes)</t>
+  </si>
+  <si>
+    <t>Unit-Tests (User, Account) / ResetPassword (Endpoint, Mail-Service)</t>
+  </si>
+  <si>
+    <t>ThemeProvider &amp; Beach-Theme / SQLite→MariaDB / MFA-Logik</t>
+  </si>
+  <si>
+    <t>DB MariaDB final / Hosting &amp; Deployment / Tests</t>
+  </si>
+  <si>
     <t>Gesamtarbeitszeit</t>
   </si>
   <si>
-    <t>1200 min</t>
-  </si>
-  <si>
-    <t>20 h</t>
+    <t>3080 min</t>
+  </si>
+  <si>
+    <t>51,3 h</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -124,12 +126,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E2F3"/>
+        <fgColor theme="3" tint="0.89999084444715716"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -189,60 +191,40 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -578,150 +560,305 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F26A550-04E7-41E1-A0A9-E176EF97C205}">
-  <dimension ref="A1:E8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="11.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="27.28515625" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="18.85546875" style="1" customWidth="1"/>
+    <col min="2" max="4" width="11.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="34" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
+    <row r="2" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="D2" s="4">
+        <v>200</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
         <v>46161</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B3" s="3">
         <v>0.75</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C3" s="3">
         <v>0.91666666666666663</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D3" s="4">
         <v>240</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+      <c r="E3" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>46162</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B4" s="3">
         <v>0.54861111111111116</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C4" s="3">
         <v>0.69444444444444442</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D4" s="4">
         <v>200</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>46163</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B5" s="3">
         <v>0.3298611111111111</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C5" s="3">
         <v>0.47916666666666669</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D5" s="4">
         <v>200</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+      <c r="E5" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>46164</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B6" s="3">
         <v>0.54861111111111116</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C6" s="3">
         <v>0.65972222222222221</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D6" s="4">
         <v>160</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+      <c r="E6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
         <v>46169</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B7" s="3">
         <v>0.54861111111111116</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C7" s="3">
         <v>0.69444444444444442</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D7" s="4">
         <v>200</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+      <c r="E7" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
         <v>46170</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B8" s="3">
         <v>0.3298611111111111</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C8" s="3">
         <v>0.47916666666666669</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D8" s="4">
         <v>200</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="E8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="8" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="D9" s="4">
+        <v>220</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="8" t="s">
+    </row>
+    <row r="10" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>46182</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D10" s="4">
+        <v>200</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="10"/>
+    </row>
+    <row r="11" spans="1:5" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.3298611111111111</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0.46875</v>
+      </c>
+      <c r="D11" s="4">
+        <v>200</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>46184</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="D12" s="4">
+        <v>240</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.67361111111111116</v>
+      </c>
+      <c r="D13" s="4">
+        <v>180</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>46191</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.3298611111111111</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.46875</v>
+      </c>
+      <c r="D14" s="4">
+        <v>200</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>46192</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="D15" s="4">
+        <v>240</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>46197</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="D16" s="4">
+        <v>200</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D17:E17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
